--- a/artfynd/A 19470-2026 artfynd.xlsx
+++ b/artfynd/A 19470-2026 artfynd.xlsx
@@ -1514,32 +1514,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133786069</v>
+        <v>133786076</v>
       </c>
       <c r="B9" t="n">
-        <v>80485</v>
+        <v>99181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760385</v>
+        <v>760345</v>
       </c>
       <c r="R9" t="n">
-        <v>7191437</v>
+        <v>7191467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133786076</v>
+        <v>133786063</v>
       </c>
       <c r="B11" t="n">
         <v>99181</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760345</v>
+        <v>760405</v>
       </c>
       <c r="R11" t="n">
-        <v>7191467</v>
+        <v>7191501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,32 +1835,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133786063</v>
+        <v>133786069</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>80485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760405</v>
+        <v>760385</v>
       </c>
       <c r="R12" t="n">
-        <v>7191501</v>
+        <v>7191437</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2164,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133786078</v>
+        <v>133786049</v>
       </c>
       <c r="B15" t="n">
         <v>99181</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760361</v>
+        <v>760243</v>
       </c>
       <c r="R15" t="n">
-        <v>7191468</v>
+        <v>7191615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,12 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Foto 5</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133786049</v>
+        <v>133786078</v>
       </c>
       <c r="B16" t="n">
         <v>99181</v>
@@ -2311,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760243</v>
+        <v>760361</v>
       </c>
       <c r="R16" t="n">
-        <v>7191615</v>
+        <v>7191468</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2351,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Foto 5</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,32 +2490,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133786039</v>
+        <v>133786070</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>80479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760165</v>
+        <v>760385</v>
       </c>
       <c r="R18" t="n">
-        <v>7191607</v>
+        <v>7191437</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,12 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Foto 1</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,53 +2597,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133786056</v>
+        <v>133786039</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760413</v>
+        <v>760165</v>
       </c>
       <c r="R19" t="n">
-        <v>7191572</v>
+        <v>7191607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,19 +2677,19 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
+          <t>Foto 1</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2722,45 +2709,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133786070</v>
+        <v>133786056</v>
       </c>
       <c r="B20" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760385</v>
+        <v>760413</v>
       </c>
       <c r="R20" t="n">
-        <v>7191437</v>
+        <v>7191572</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,14 +2797,19 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133786059</v>
+        <v>133786086</v>
       </c>
       <c r="B32" t="n">
-        <v>99181</v>
+        <v>80479</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>760421</v>
+        <v>760278</v>
       </c>
       <c r="R32" t="n">
-        <v>7191549</v>
+        <v>7191593</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,32 +4131,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133786086</v>
+        <v>133786059</v>
       </c>
       <c r="B33" t="n">
-        <v>80479</v>
+        <v>99181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760278</v>
+        <v>760421</v>
       </c>
       <c r="R33" t="n">
-        <v>7191593</v>
+        <v>7191549</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4345,53 +4345,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133786081</v>
+        <v>133786045</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760323</v>
+        <v>760229</v>
       </c>
       <c r="R35" t="n">
-        <v>7191534</v>
+        <v>7191628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4423,7 +4415,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4433,19 +4425,14 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4465,45 +4452,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133786045</v>
+        <v>133786081</v>
       </c>
       <c r="B36" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760229</v>
+        <v>760323</v>
       </c>
       <c r="R36" t="n">
-        <v>7191628</v>
+        <v>7191534</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4535,7 +4530,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4545,14 +4540,19 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133786068</v>
+        <v>133786053</v>
       </c>
       <c r="B37" t="n">
-        <v>80474</v>
+        <v>91960</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760385</v>
+        <v>760339</v>
       </c>
       <c r="R37" t="n">
-        <v>7191437</v>
+        <v>7191617</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,12 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4684,10 +4679,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133786053</v>
+        <v>133786068</v>
       </c>
       <c r="B38" t="n">
-        <v>91960</v>
+        <v>80474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4695,21 +4690,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4719,10 +4714,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760339</v>
+        <v>760385</v>
       </c>
       <c r="R38" t="n">
-        <v>7191617</v>
+        <v>7191437</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4754,7 +4749,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4764,7 +4759,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4791,32 +4791,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133786085</v>
+        <v>133786051</v>
       </c>
       <c r="B39" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>760278</v>
+        <v>760269</v>
       </c>
       <c r="R39" t="n">
-        <v>7191593</v>
+        <v>7191649</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,32 +4898,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133786051</v>
+        <v>133786085</v>
       </c>
       <c r="B40" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760269</v>
+        <v>760278</v>
       </c>
       <c r="R40" t="n">
-        <v>7191649</v>
+        <v>7191593</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 19470-2026 artfynd.xlsx
+++ b/artfynd/A 19470-2026 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>133786050</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,32 +1514,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133786076</v>
+        <v>133786069</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>80492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760345</v>
+        <v>760385</v>
       </c>
       <c r="R9" t="n">
-        <v>7191467</v>
+        <v>7191437</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,7 +1624,7 @@
         <v>133786041</v>
       </c>
       <c r="B10" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133786063</v>
+        <v>133786076</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760405</v>
+        <v>760345</v>
       </c>
       <c r="R11" t="n">
-        <v>7191501</v>
+        <v>7191467</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,32 +1835,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133786069</v>
+        <v>133786063</v>
       </c>
       <c r="B12" t="n">
-        <v>80485</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760385</v>
+        <v>760405</v>
       </c>
       <c r="R12" t="n">
-        <v>7191437</v>
+        <v>7191501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,7 +2060,7 @@
         <v>133786075</v>
       </c>
       <c r="B14" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133786049</v>
+        <v>133786078</v>
       </c>
       <c r="B15" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760243</v>
+        <v>760361</v>
       </c>
       <c r="R15" t="n">
-        <v>7191615</v>
+        <v>7191468</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2244,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Foto 5</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133786078</v>
+        <v>133786049</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760361</v>
+        <v>760243</v>
       </c>
       <c r="R16" t="n">
-        <v>7191468</v>
+        <v>7191615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,12 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Foto 5</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,7 +2386,7 @@
         <v>133786067</v>
       </c>
       <c r="B17" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,32 +2490,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133786070</v>
+        <v>133786039</v>
       </c>
       <c r="B18" t="n">
-        <v>80479</v>
+        <v>99188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760385</v>
+        <v>760165</v>
       </c>
       <c r="R18" t="n">
-        <v>7191437</v>
+        <v>7191607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2570,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Foto 1</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,45 +2602,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133786039</v>
+        <v>133786056</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760165</v>
+        <v>760413</v>
       </c>
       <c r="R19" t="n">
-        <v>7191607</v>
+        <v>7191572</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,19 +2690,19 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Foto 1</t>
+          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2709,53 +2722,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133786056</v>
+        <v>133786070</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>80486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760413</v>
+        <v>760385</v>
       </c>
       <c r="R20" t="n">
-        <v>7191572</v>
+        <v>7191437</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2792,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2797,19 +2802,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>133786064</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>133786087</v>
       </c>
       <c r="B22" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>133786072</v>
       </c>
       <c r="B23" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>133786040</v>
       </c>
       <c r="B25" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>133786084</v>
       </c>
       <c r="B26" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>133786048</v>
       </c>
       <c r="B27" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>133786066</v>
       </c>
       <c r="B28" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>133786047</v>
       </c>
       <c r="B29" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>133786079</v>
       </c>
       <c r="B30" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>133786065</v>
       </c>
       <c r="B31" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133786086</v>
+        <v>133786059</v>
       </c>
       <c r="B32" t="n">
-        <v>80479</v>
+        <v>99188</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>760278</v>
+        <v>760421</v>
       </c>
       <c r="R32" t="n">
-        <v>7191593</v>
+        <v>7191549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,32 +4131,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133786059</v>
+        <v>133786086</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>80486</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760421</v>
+        <v>760278</v>
       </c>
       <c r="R33" t="n">
-        <v>7191549</v>
+        <v>7191593</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4241,7 +4241,7 @@
         <v>133786042</v>
       </c>
       <c r="B34" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,45 +4345,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133786045</v>
+        <v>133786081</v>
       </c>
       <c r="B35" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760229</v>
+        <v>760323</v>
       </c>
       <c r="R35" t="n">
-        <v>7191628</v>
+        <v>7191534</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4415,7 +4423,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4425,14 +4433,19 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4452,53 +4465,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133786081</v>
+        <v>133786045</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>99188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760323</v>
+        <v>760229</v>
       </c>
       <c r="R36" t="n">
-        <v>7191534</v>
+        <v>7191628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4530,7 +4535,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4540,19 +4545,14 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133786053</v>
+        <v>133786068</v>
       </c>
       <c r="B37" t="n">
-        <v>91960</v>
+        <v>80481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760339</v>
+        <v>760385</v>
       </c>
       <c r="R37" t="n">
-        <v>7191617</v>
+        <v>7191437</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4679,10 +4684,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133786068</v>
+        <v>133786053</v>
       </c>
       <c r="B38" t="n">
-        <v>80474</v>
+        <v>91967</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4690,21 +4695,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760385</v>
+        <v>760339</v>
       </c>
       <c r="R38" t="n">
-        <v>7191437</v>
+        <v>7191617</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,7 +4754,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4759,12 +4764,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4791,32 +4791,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133786051</v>
+        <v>133786085</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>760269</v>
+        <v>760278</v>
       </c>
       <c r="R39" t="n">
-        <v>7191649</v>
+        <v>7191593</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,32 +4898,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133786085</v>
+        <v>133786051</v>
       </c>
       <c r="B40" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760278</v>
+        <v>760269</v>
       </c>
       <c r="R40" t="n">
-        <v>7191593</v>
+        <v>7191649</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 19470-2026 artfynd.xlsx
+++ b/artfynd/A 19470-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1926196</v>
+        <v>142815</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759884.615211423</v>
+        <v>759887</v>
       </c>
       <c r="R2" t="n">
-        <v>7190982.061911093</v>
+        <v>7190999</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,11 +760,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gammal jättelik sälg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>142815</v>
+        <v>133786053</v>
       </c>
       <c r="B3" t="n">
-        <v>89337</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelmyran, Vb</t>
+          <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759887.4426763775</v>
+        <v>760339</v>
       </c>
       <c r="R3" t="n">
-        <v>7190999.041919189</v>
+        <v>7191617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,36 +868,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1926195</v>
+        <v>404406</v>
       </c>
       <c r="B4" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelmyran, Vb</t>
+          <t>Krångbäcken nordost Gammelmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760009.8712752119</v>
+        <v>760289</v>
       </c>
       <c r="R4" t="n">
-        <v>7190939.68942402</v>
+        <v>7191595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,21 +952,11 @@
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,9 +971,14 @@
           <t>Blandskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blöt sumpskog</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>gammal jättelik sälg</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1926197</v>
+        <v>133786038</v>
       </c>
       <c r="B5" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelmyran, Vb</t>
+          <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760113.1129600722</v>
+        <v>760129</v>
       </c>
       <c r="R5" t="n">
-        <v>7190992.826211208</v>
+        <v>7191612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,41 +1087,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>gammal jättelik sälg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2057438</v>
+        <v>133786044</v>
       </c>
       <c r="B6" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammelmyran, Vb</t>
+          <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760113.1129600722</v>
+        <v>760218</v>
       </c>
       <c r="R6" t="n">
-        <v>7190992.826211208</v>
+        <v>7191567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,76 +1194,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gammal jättelik sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>404406</v>
+        <v>133786058</v>
       </c>
       <c r="B7" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krångbäcken nordost Gammelmyran, Vb</t>
+          <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760288.6397119666</v>
+        <v>760416</v>
       </c>
       <c r="R7" t="n">
-        <v>7191595.011347764</v>
+        <v>7191564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,63 +1301,48 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blöt sumpskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133786050</v>
+        <v>133786060</v>
       </c>
       <c r="B8" t="n">
-        <v>99188</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760256</v>
+        <v>760449</v>
       </c>
       <c r="R8" t="n">
-        <v>7191633</v>
+        <v>7191553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133786069</v>
+        <v>133786061</v>
       </c>
       <c r="B9" t="n">
-        <v>80492</v>
+        <v>96410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760385</v>
+        <v>760407</v>
       </c>
       <c r="R9" t="n">
-        <v>7191437</v>
+        <v>7191489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133786041</v>
+        <v>133786077</v>
       </c>
       <c r="B10" t="n">
-        <v>99188</v>
+        <v>96410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760187</v>
+        <v>760365</v>
       </c>
       <c r="R10" t="n">
-        <v>7191579</v>
+        <v>7191468</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133786076</v>
+        <v>133786080</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>96410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1763,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760345</v>
+        <v>760350</v>
       </c>
       <c r="R11" t="n">
-        <v>7191467</v>
+        <v>7191499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133786063</v>
+        <v>133786082</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760405</v>
+        <v>760325</v>
       </c>
       <c r="R12" t="n">
-        <v>7191501</v>
+        <v>7191552</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,53 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133786073</v>
+        <v>1926194</v>
       </c>
       <c r="B13" t="n">
-        <v>58349</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Krångbäcken, Vb</t>
+          <t>Gammelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760380</v>
+        <v>760006</v>
       </c>
       <c r="R13" t="n">
-        <v>7191416</v>
+        <v>7190917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,22 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,61 +1933,71 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>gammal jättelik sälg</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133786075</v>
+        <v>1926195</v>
       </c>
       <c r="B14" t="n">
-        <v>99188</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Krångbäcken, Vb</t>
+          <t>Gammelmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760348</v>
+        <v>760010</v>
       </c>
       <c r="R14" t="n">
-        <v>7191355</v>
+        <v>7190940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,22 +2024,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,61 +2040,71 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>gammal jättelik sälg</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133786078</v>
+        <v>1926196</v>
       </c>
       <c r="B15" t="n">
-        <v>99188</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krångbäcken, Vb</t>
+          <t>Gammelmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760361</v>
+        <v>759885</v>
       </c>
       <c r="R15" t="n">
-        <v>7191468</v>
+        <v>7190982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,27 +2131,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Foto 5</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,61 +2147,71 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>gammal jättelik sälg</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133786049</v>
+        <v>1926197</v>
       </c>
       <c r="B16" t="n">
-        <v>99188</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krångbäcken, Vb</t>
+          <t>Gammelmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760243</v>
+        <v>760113</v>
       </c>
       <c r="R16" t="n">
-        <v>7191615</v>
+        <v>7190993</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,22 +2238,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,48 +2254,58 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>gammal jättelik sälg</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133786067</v>
+        <v>133786068</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2418,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>760383</v>
+        <v>760385</v>
       </c>
       <c r="R17" t="n">
-        <v>7191457</v>
+        <v>7191437</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2360,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,32 +2392,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133786039</v>
+        <v>133786085</v>
       </c>
       <c r="B18" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760165</v>
+        <v>760278</v>
       </c>
       <c r="R18" t="n">
-        <v>7191607</v>
+        <v>7191593</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,12 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Foto 1</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,53 +2499,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133786056</v>
+        <v>2057438</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Krångbäcken, Vb</t>
+          <t>Gammelmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760413</v>
+        <v>760113</v>
       </c>
       <c r="R19" t="n">
-        <v>7191572</v>
+        <v>7190993</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,47 +2564,42 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
+          <t>2008-09-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>gammal jättelik sälg</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2725,7 +2609,7 @@
         <v>133786070</v>
       </c>
       <c r="B20" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133786064</v>
+        <v>133786086</v>
       </c>
       <c r="B21" t="n">
-        <v>99188</v>
+        <v>80493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2864,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>760418</v>
+        <v>760278</v>
       </c>
       <c r="R21" t="n">
-        <v>7191499</v>
+        <v>7191593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,32 +2820,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133786087</v>
+        <v>133786069</v>
       </c>
       <c r="B22" t="n">
-        <v>99188</v>
+        <v>80499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2971,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760236</v>
+        <v>760385</v>
       </c>
       <c r="R22" t="n">
-        <v>7191634</v>
+        <v>7191437</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3016,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3043,32 +2927,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133786072</v>
+        <v>133786084</v>
       </c>
       <c r="B23" t="n">
-        <v>99188</v>
+        <v>80500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760380</v>
+        <v>760278</v>
       </c>
       <c r="R23" t="n">
-        <v>7191416</v>
+        <v>7191593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3007,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3270,45 +3154,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133786040</v>
+        <v>133786056</v>
       </c>
       <c r="B25" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>760170</v>
+        <v>760413</v>
       </c>
       <c r="R25" t="n">
-        <v>7191592</v>
+        <v>7191572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,19 +3242,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Foto 2</t>
+          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3382,45 +3274,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133786084</v>
+        <v>133786081</v>
       </c>
       <c r="B26" t="n">
-        <v>80493</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>760278</v>
+        <v>760323</v>
       </c>
       <c r="R26" t="n">
-        <v>7191593</v>
+        <v>7191534</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,7 +3352,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,14 +3362,19 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3489,45 +3394,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133786048</v>
+        <v>133786054</v>
       </c>
       <c r="B27" t="n">
-        <v>99188</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>760230</v>
+        <v>760346</v>
       </c>
       <c r="R27" t="n">
-        <v>7191608</v>
+        <v>7191614</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3559,7 +3472,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3482,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,45 +3514,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133786066</v>
+        <v>133786073</v>
       </c>
       <c r="B28" t="n">
-        <v>99188</v>
+        <v>58349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>760388</v>
+        <v>760380</v>
       </c>
       <c r="R28" t="n">
-        <v>7191473</v>
+        <v>7191416</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3666,7 +3592,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3676,7 +3602,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,10 +3629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133786047</v>
+        <v>133786039</v>
       </c>
       <c r="B29" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,10 +3664,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>760222</v>
+        <v>760165</v>
       </c>
       <c r="R29" t="n">
-        <v>7191616</v>
+        <v>7191607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3773,7 +3699,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3783,7 +3709,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Foto 1</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,10 +3741,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133786079</v>
+        <v>133786040</v>
       </c>
       <c r="B30" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,10 +3776,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>760360</v>
+        <v>760170</v>
       </c>
       <c r="R30" t="n">
-        <v>7191474</v>
+        <v>7191592</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3880,7 +3811,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3821,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3917,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133786065</v>
+        <v>133786041</v>
       </c>
       <c r="B31" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3952,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>760391</v>
+        <v>760187</v>
       </c>
       <c r="R31" t="n">
-        <v>7191480</v>
+        <v>7191579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3987,7 +3923,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3997,7 +3933,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4024,10 +3960,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133786059</v>
+        <v>133786042</v>
       </c>
       <c r="B32" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,10 +3995,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>760421</v>
+        <v>760183</v>
       </c>
       <c r="R32" t="n">
-        <v>7191549</v>
+        <v>7191584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4094,7 +4030,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4104,7 +4040,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,32 +4067,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133786086</v>
+        <v>133786043</v>
       </c>
       <c r="B33" t="n">
-        <v>80486</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4166,10 +4102,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760278</v>
+        <v>760216</v>
       </c>
       <c r="R33" t="n">
-        <v>7191593</v>
+        <v>7191578</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4201,7 +4137,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4211,7 +4147,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,10 +4174,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133786042</v>
+        <v>133786045</v>
       </c>
       <c r="B34" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4273,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760183</v>
+        <v>760229</v>
       </c>
       <c r="R34" t="n">
-        <v>7191584</v>
+        <v>7191628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4308,7 +4244,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4318,7 +4254,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,53 +4281,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133786081</v>
+        <v>133786047</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760323</v>
+        <v>760222</v>
       </c>
       <c r="R35" t="n">
-        <v>7191534</v>
+        <v>7191616</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4423,7 +4351,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4433,19 +4361,14 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bortfläkta barkfläckar långt ned på stammen av gamla granar. Typiskt för tretå, men svårt att helt utesluta andra hackspettar + svårt att åldersbestämma</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4465,10 +4388,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133786045</v>
+        <v>133786048</v>
       </c>
       <c r="B36" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,10 +4423,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760229</v>
+        <v>760230</v>
       </c>
       <c r="R36" t="n">
-        <v>7191628</v>
+        <v>7191608</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4535,7 +4458,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4545,7 +4468,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4572,32 +4495,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133786068</v>
+        <v>133786049</v>
       </c>
       <c r="B37" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4607,10 +4530,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760385</v>
+        <v>760243</v>
       </c>
       <c r="R37" t="n">
-        <v>7191437</v>
+        <v>7191615</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4642,7 +4565,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,12 +4575,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4684,32 +4602,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133786053</v>
+        <v>133786050</v>
       </c>
       <c r="B38" t="n">
-        <v>91967</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4719,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760339</v>
+        <v>760256</v>
       </c>
       <c r="R38" t="n">
-        <v>7191617</v>
+        <v>7191633</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4754,7 +4672,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4764,7 +4682,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4791,32 +4709,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133786085</v>
+        <v>133786051</v>
       </c>
       <c r="B39" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4744,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>760278</v>
+        <v>760269</v>
       </c>
       <c r="R39" t="n">
-        <v>7191593</v>
+        <v>7191649</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4779,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,7 +4789,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,10 +4816,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133786051</v>
+        <v>133786059</v>
       </c>
       <c r="B40" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4933,10 +4851,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760269</v>
+        <v>760421</v>
       </c>
       <c r="R40" t="n">
-        <v>7191649</v>
+        <v>7191549</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4968,7 +4886,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4978,7 +4896,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5005,53 +4923,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133786054</v>
+        <v>133786063</v>
       </c>
       <c r="B41" t="n">
-        <v>57162</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Krångbäcken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760346</v>
+        <v>760405</v>
       </c>
       <c r="R41" t="n">
-        <v>7191614</v>
+        <v>7191501</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5083,7 +4993,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5093,12 +5003,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,6 +5027,1081 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133786064</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>760418</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7191499</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133786065</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>760391</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7191480</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133786066</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>760388</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7191473</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133786067</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>760383</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7191457</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133786072</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>760380</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7191416</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133786075</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>760348</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7191355</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>133786076</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>760345</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7191467</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>133786078</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>760361</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7191468</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Foto 5</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>133786079</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>760360</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7191474</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133786087</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Krångbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>760236</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7191634</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19470-2026 artfynd.xlsx
+++ b/artfynd/A 19470-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/404406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786044</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786058</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786060</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786061</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786077</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786080</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786082</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1926194</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1926195</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1926196</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1926197</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786085</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2057438</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786070</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786086</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786069</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786084</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3151,6 +3266,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786052</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3271,6 +3391,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786056</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3391,6 +3516,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786081</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3511,6 +3641,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786054</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3626,6 +3761,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786073</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3738,6 +3878,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786039</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3850,6 +3995,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786040</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3957,6 +4107,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786041</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4064,6 +4219,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786042</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4171,6 +4331,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786043</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4278,6 +4443,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786045</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4385,6 +4555,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786047</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4492,6 +4667,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786048</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4599,6 +4779,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786049</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4706,6 +4891,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786050</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4813,6 +5003,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786051</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4920,6 +5115,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786059</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5027,6 +5227,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786063</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5134,6 +5339,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786064</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5241,6 +5451,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786065</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5348,6 +5563,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786066</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5455,6 +5675,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786067</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5562,6 +5787,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786072</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5669,6 +5899,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786075</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5776,6 +6011,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786076</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5888,6 +6128,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786078</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5995,6 +6240,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786079</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6102,8 +6352,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>